--- a/Create_order/Excel Source/channel_ienh.xlsx
+++ b/Create_order/Excel Source/channel_ienh.xlsx
@@ -1884,7 +1884,7 @@
         <v>32</v>
       </c>
       <c r="G8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:7">
@@ -1907,7 +1907,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:7">
@@ -1930,7 +1930,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="15.6" spans="1:7">
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="15.6" spans="1:7">
@@ -2344,7 +2344,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="15.6" spans="1:7">
@@ -2367,7 +2367,7 @@
         <v>3</v>
       </c>
       <c r="G29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="15.6" spans="1:7">
@@ -2390,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" ht="15.6" spans="1:7">
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.6" spans="1:7">
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="15.6" spans="1:7">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" ht="15.6" spans="1:7">
@@ -2505,7 +2505,7 @@
         <v>114</v>
       </c>
       <c r="G35" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="15.6" spans="1:7">
@@ -2574,7 +2574,7 @@
         <v>124</v>
       </c>
       <c r="G38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" ht="15.6" spans="1:7">
@@ -2712,7 +2712,7 @@
         <v>144</v>
       </c>
       <c r="G44" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" ht="15.6" spans="1:7">

--- a/Create_order/Excel Source/channel_ienh.xlsx
+++ b/Create_order/Excel Source/channel_ienh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12420"/>
+    <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -1976,7 +1976,7 @@
         <v>47</v>
       </c>
       <c r="G12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:7">

--- a/Create_order/Excel Source/channel_ienh.xlsx
+++ b/Create_order/Excel Source/channel_ienh.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$G$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="168">
   <si>
     <t>ID</t>
   </si>
@@ -481,6 +481,51 @@
   </si>
   <si>
     <t>STCPAY</t>
+  </si>
+  <si>
+    <t>WowPay</t>
+  </si>
+  <si>
+    <t>WowpayWallet</t>
+  </si>
+  <si>
+    <t>Wallet_Vadofone</t>
+  </si>
+  <si>
+    <t>ClipsPay</t>
+  </si>
+  <si>
+    <t>ClipsPayVodafone</t>
+  </si>
+  <si>
+    <t>VODPAY</t>
+  </si>
+  <si>
+    <t>ClipsPayFawryPay</t>
+  </si>
+  <si>
+    <t>FAWRYPAY</t>
+  </si>
+  <si>
+    <t>ClipsPaySTCPAY</t>
+  </si>
+  <si>
+    <t>StcPay</t>
+  </si>
+  <si>
+    <t>ClipsPaySACARD</t>
+  </si>
+  <si>
+    <t>LocalCard</t>
+  </si>
+  <si>
+    <t>SACARD</t>
+  </si>
+  <si>
+    <t>ClipsPayAECARD</t>
+  </si>
+  <si>
+    <t>AECARD</t>
   </si>
   <si>
     <t>暂时还没有</t>
@@ -1695,8 +1740,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G47"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="12.2222222222222" customWidth="1"/>
@@ -1815,7 +1860,7 @@
         <v>21</v>
       </c>
       <c r="G5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:7">
@@ -2298,7 +2343,7 @@
         <v>25</v>
       </c>
       <c r="G26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="15.6" spans="1:7">
@@ -2482,7 +2527,7 @@
         <v>111</v>
       </c>
       <c r="G34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="15.6" spans="1:7">
@@ -2528,7 +2573,7 @@
         <v>118</v>
       </c>
       <c r="G36" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="15.6" spans="1:7">
@@ -2666,7 +2711,7 @@
         <v>138</v>
       </c>
       <c r="G42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="15.6" spans="1:7">
@@ -2735,7 +2780,7 @@
         <v>25</v>
       </c>
       <c r="G45" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" ht="15.6" spans="1:7">
@@ -2758,7 +2803,7 @@
         <v>25</v>
       </c>
       <c r="G46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15.6" spans="1:7">
@@ -2781,11 +2826,149 @@
         <v>149</v>
       </c>
       <c r="G47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.6" spans="1:7">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.6" spans="1:7">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="15.6" spans="1:7">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G50" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="15.6" spans="1:7">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G51" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="15.6" spans="1:7">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="15.6" spans="1:7">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G53" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G47" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G50" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2795,7 +2978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <cols>
@@ -3541,7 +3724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3564,7 +3747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3587,7 +3770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:8">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3610,7 +3793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:8">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3656,10 +3839,10 @@
         <v>1</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3705,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3731,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3745,7 +3928,7 @@
         <v>131</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>133</v>
@@ -3757,10 +3940,10 @@
         <v>1</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3771,7 +3954,7 @@
         <v>135</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>137</v>
@@ -3806,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3832,7 +4015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:8">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3855,7 +4038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:8">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -3878,7 +4061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:8">
       <c r="A47" s="3">
         <v>46</v>
       </c>
